--- a/自考本科/承办主考学校/主考学校对比.xlsx
+++ b/自考本科/承办主考学校/主考学校对比.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>深圳大学</t>
   </si>
@@ -45,6 +45,15 @@
     <t>实践考试</t>
   </si>
   <si>
+    <t>报考方式</t>
+  </si>
+  <si>
+    <t>线上+邮寄</t>
+  </si>
+  <si>
+    <t>线上</t>
+  </si>
+  <si>
     <t>是否要求笔试成绩合格</t>
   </si>
   <si>
@@ -69,6 +78,9 @@
     <t>四月、？</t>
   </si>
   <si>
+    <t>？、七月</t>
+  </si>
+  <si>
     <t>考试时间</t>
   </si>
   <si>
@@ -84,23 +96,25 @@
     <t>十月、明年四月</t>
   </si>
   <si>
+    <t>？、九月</t>
+  </si>
+  <si>
+    <t>考试形式</t>
+  </si>
+  <si>
+    <t>上机</t>
+  </si>
+  <si>
+    <t>上机+纸笔</t>
+  </si>
+  <si>
+    <t>？</t>
+  </si>
+  <si>
     <t>考试大纲</t>
   </si>
   <si>
-    <t>？</t>
-  </si>
-  <si>
-    <t>考试形式</t>
-  </si>
-  <si>
-    <t>上机</t>
-  </si>
-  <si>
-    <t>上机+纸笔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是否携带教材
-（就算能带资料，建议也只带自考教材）</t>
+    <t>是否开卷考试（能带教材）</t>
   </si>
   <si>
     <t>全部开卷</t>
@@ -115,15 +129,6 @@
     <t>部分开卷</t>
   </si>
   <si>
-    <t>报考方式</t>
-  </si>
-  <si>
-    <t>线上+邮寄</t>
-  </si>
-  <si>
-    <t>线上</t>
-  </si>
-  <si>
     <t>实践考试培训</t>
   </si>
   <si>
@@ -164,7 +169,7 @@
   </si>
   <si>
     <t xml:space="preserve">毕业申请方式
-（统一为考试院）</t>
+（统一为广东教育考试院）</t>
   </si>
   <si>
     <t>学位</t>
@@ -191,19 +196,32 @@
     <t>最大查重率要求</t>
   </si>
   <si>
+    <t>线上+线下</t>
+  </si>
+  <si>
+    <t>官网下载文件名字相同</t>
+  </si>
+  <si>
     <t>官网信息质量</t>
   </si>
   <si>
     <t>信息发布在两个网站，信息过于分散没有以附件的形式发布</t>
   </si>
   <si>
+    <t>没有学位相关公告，没有学士学位授予工作细则</t>
+  </si>
+  <si>
     <t>过于简洁</t>
   </si>
   <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>学位论文不符合规范可以暂缓毕业</t>
+    <t xml:space="preserve">过于简洁
+经常无法连接</t>
+  </si>
+  <si>
+    <t>说明1</t>
+  </si>
+  <si>
+    <t>实践考试材料提交经常只在要提交的前一天才发公告</t>
   </si>
   <si>
     <t xml:space="preserve">实践考试不能一次考五科
@@ -211,13 +229,15 @@
 有一个公开的毕业考生QQ群</t>
   </si>
   <si>
-    <t xml:space="preserve">实践考核成绩（非百分制成绩）折算规则：优秀=95 分、
-良好=85 分、中等=75 分、及格=65 分；</t>
+    <t xml:space="preserve">实践考核成绩（非百分制成绩）折算规则：优秀=95 分、良好=85 分、中等=75 分、及格=65 分；</t>
   </si>
   <si>
     <t>没有《广东金融学院成人高等教育本科毕业生学士学位授予工作细则》</t>
   </si>
   <si>
+    <t>说明2</t>
+  </si>
+  <si>
     <t>从实践课程清单可以看出考试形式</t>
   </si>
   <si>
@@ -228,6 +248,9 @@
   </si>
   <si>
     <t>从实践大纲可以考出考试形式、部分开卷</t>
+  </si>
+  <si>
+    <t>今年下半年才新开考计算机实践，新学校容易踩坑</t>
   </si>
 </sst>
 </file>
@@ -247,15 +270,27 @@
       <name val="等距更纱黑体 SC Light"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -272,47 +307,50 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255" vertical="center"/>
-    </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255" vertical="center"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255" vertical="center"/>
+    <xf fontId="1" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255" vertical="center"/>
+    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -813,309 +851,331 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.140625"/>
-    <col customWidth="1" min="2" max="2" style="1" width="22.7109375"/>
-    <col customWidth="1" min="3" max="15" style="1" width="20.7109375"/>
+    <col customWidth="1" min="1" max="1" style="1" width="5.00390625"/>
+    <col customWidth="1" min="2" max="2" style="2" width="25.421875"/>
+    <col customWidth="1" min="3" max="10" style="1" width="17.57421875"/>
+    <col customWidth="1" min="11" max="15" style="1" width="20.7109375"/>
     <col min="16" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
+    <row r="1" s="3" customFormat="1" ht="15.75">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
     </row>
     <row r="2" ht="15.75">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
     </row>
     <row r="3" ht="15.75">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75">
+      <c r="A4" s="6"/>
+      <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" ht="15.75">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="H4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="J4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="1" t="s">
+    </row>
+    <row r="5" ht="15.75">
+      <c r="A5" s="6"/>
+      <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" ht="15.75">
-      <c r="A6" s="2"/>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
+      <c r="A6" s="6"/>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" ht="47.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75">
+      <c r="A7" s="6"/>
+      <c r="B7" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" ht="31.5">
+      <c r="A8" s="6"/>
+      <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>34</v>
+      <c r="D8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>34</v>
+      <c r="G8" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
     </row>
     <row r="9" ht="15.75">
-      <c r="A9" s="2"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
+      <c r="A9" s="6"/>
     </row>
     <row r="10" ht="15.75">
-      <c r="A10" s="2"/>
-      <c r="B10" s="1" t="s">
-        <v>35</v>
+      <c r="A10" s="6"/>
+      <c r="B10" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
     </row>
     <row r="11" ht="15.75">
-      <c r="A11" s="2"/>
-      <c r="B11" s="1" t="s">
-        <v>36</v>
+      <c r="A11" s="6"/>
+      <c r="B11" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1">
         <v>1800</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" ht="15.75">
-      <c r="A12" s="2"/>
-      <c r="B12" s="1" t="s">
-        <v>37</v>
+      <c r="A12" s="6"/>
+      <c r="B12" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1131,46 +1191,48 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
     </row>
-    <row r="13" s="5" customFormat="1" ht="15.75">
-      <c r="A13" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="5" t="s">
+    <row r="13" s="9" customFormat="1" ht="15.75">
+      <c r="A13" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="B13" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="C13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-    </row>
-    <row r="14" ht="15.75">
-      <c r="A14" s="7"/>
-      <c r="B14" s="1" t="s">
+      <c r="E13" s="12" t="s">
         <v>43</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="15.75">
+      <c r="A14" s="6"/>
+      <c r="B14" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="C14" s="1">
         <v>1500</v>
@@ -1182,10 +1244,10 @@
         <v>1500</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="1">
-        <v>400</v>
+        <v>30</v>
+      </c>
+      <c r="G14" s="7">
+        <v>800</v>
       </c>
       <c r="H14" s="1">
         <v>1500</v>
@@ -1193,7 +1255,9 @@
       <c r="I14" s="1">
         <v>1000</v>
       </c>
-      <c r="J14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1201,16 +1265,16 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
     </row>
-    <row r="15" ht="15.75">
-      <c r="A15" s="7"/>
-      <c r="B15" s="1" t="s">
-        <v>44</v>
+    <row r="15" s="1" customFormat="1" ht="15.75">
+      <c r="A15" s="6"/>
+      <c r="B15" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -1225,86 +1289,102 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
     </row>
-    <row r="16" ht="15.75">
-      <c r="A16" s="7"/>
-      <c r="B16" s="1" t="s">
-        <v>47</v>
+    <row r="16" s="1" customFormat="1" ht="15.75">
+      <c r="A16" s="6"/>
+      <c r="B16" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" ht="31.5">
-      <c r="A17" s="7"/>
-      <c r="B17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" s="5" customFormat="1" ht="15.75">
-      <c r="A18" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="47.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+    </row>
+    <row r="18" s="9" customFormat="1" ht="15.75">
+      <c r="A18" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="12">
         <v>60</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="9">
         <v>70</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>23</v>
+      <c r="E18" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="G18" s="9">
         <v>65</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="9">
         <v>70</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="9">
         <v>70</v>
       </c>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
+      <c r="J18" s="9">
+        <v>60</v>
+      </c>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
     </row>
     <row r="19" ht="15.75">
-      <c r="A19" s="2"/>
-      <c r="B19" s="1" t="s">
-        <v>51</v>
+      <c r="A19" s="6"/>
+      <c r="B19" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="C19" s="1">
         <v>70</v>
@@ -1312,53 +1392,59 @@
       <c r="D19" s="1">
         <v>70</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>52</v>
+      <c r="E19" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="F19" s="1">
         <v>70</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>52</v>
+      <c r="G19" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="20" ht="15.75">
-      <c r="A20" s="2"/>
-      <c r="B20" s="1" t="s">
-        <v>55</v>
+      <c r="A20" s="6"/>
+      <c r="B20" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="21" ht="15.75">
-      <c r="A21" s="2"/>
-      <c r="B21" s="1" t="s">
-        <v>56</v>
+      <c r="A21" s="6"/>
+      <c r="B21" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="C21" s="1">
         <v>20</v>
@@ -1367,13 +1453,13 @@
         <v>30</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" s="1">
+        <v>30</v>
+      </c>
+      <c r="F21" s="8">
         <v>10</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H21" s="1">
         <v>25</v>
@@ -1381,7 +1467,9 @@
       <c r="I21" s="1">
         <v>30</v>
       </c>
-      <c r="J21" s="1"/>
+      <c r="J21" s="1">
+        <v>25</v>
+      </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -1390,111 +1478,162 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" ht="15.75">
-      <c r="A22" s="2"/>
-      <c r="B22" s="1" t="s">
-        <v>32</v>
+      <c r="A22" s="6"/>
+      <c r="B22" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" s="9" customFormat="1" ht="47.25">
+        <v>10</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" s="9" customFormat="1" ht="15.75">
       <c r="A23" s="9"/>
-      <c r="B23" s="9" t="s">
-        <v>57</v>
+      <c r="B23" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
+        <v>14</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="I23" s="9" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
       <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-    </row>
-    <row r="24" s="3" customFormat="1" ht="94.5">
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3" t="s">
+    </row>
+    <row r="24" s="1" customFormat="1" ht="63">
+      <c r="A24" s="1"/>
+      <c r="B24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="C24" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" s="3" customFormat="1" ht="31.5">
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3" t="s">
+      <c r="J24" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="94.5">
+      <c r="A25" s="1"/>
+      <c r="B25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3" t="s">
+      <c r="C25" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
+      <c r="H25" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="47.25">
+      <c r="B26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" ht="63">
+      <c r="J27" s="1" t="s">
+        <v>76</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A8"/>
+  <mergeCells count="4">
+    <mergeCell ref="A2:A12"/>
     <mergeCell ref="A13:A17"/>
+    <mergeCell ref="C17:J17"/>
     <mergeCell ref="A18:A22"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>

--- a/自考本科/承办主考学校/主考学校对比.xlsx
+++ b/自考本科/承办主考学校/主考学校对比.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>深圳大学</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>从实践大纲可以考出考试形式、部分开卷</t>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>今年下半年才新开考计算机实践，新学校容易踩坑</t>
@@ -270,7 +273,7 @@
       <name val="等距更纱黑体 SC Light"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,6 +290,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
   </fills>
@@ -311,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -336,6 +345,9 @@
     </xf>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1116,12 +1128,10 @@
     </row>
     <row r="10" ht="15.75">
       <c r="A10" s="6"/>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1131,18 +1141,10 @@
       <c r="F10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1152,26 +1154,22 @@
     </row>
     <row r="11" ht="15.75">
       <c r="A11" s="6"/>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="9" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="D11" s="1"/>
       <c r="E11" s="1">
         <v>1800</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" ht="15.75">
       <c r="A12" s="6"/>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1191,43 +1189,43 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
     </row>
-    <row r="13" s="9" customFormat="1" ht="15.75">
-      <c r="A13" s="10" t="s">
+    <row r="13" s="10" customFormat="1" ht="15.75">
+      <c r="A13" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="15.75">
       <c r="A14" s="6"/>
@@ -1329,57 +1327,57 @@
       <c r="B17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" s="9" customFormat="1" ht="15.75">
-      <c r="A18" s="10" t="s">
+    <row r="18" s="10" customFormat="1" ht="15.75">
+      <c r="A18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="13">
         <v>60</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="10">
         <v>70</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G18" s="9">
+      <c r="E18" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="10">
         <v>65</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="10">
         <v>70</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="10">
         <v>70</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="10">
         <v>60</v>
       </c>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
     </row>
     <row r="19" ht="15.75">
       <c r="A19" s="6"/>
@@ -1507,40 +1505,40 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" s="9" customFormat="1" ht="15.75">
-      <c r="A23" s="9"/>
-      <c r="B23" s="11" t="s">
+    <row r="23" s="10" customFormat="1" ht="15.75">
+      <c r="A23" s="10"/>
+      <c r="B23" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="9" t="s">
+      <c r="D23" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G23" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="9" t="s">
+      <c r="G23" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
+      <c r="I23" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="63">
       <c r="A24" s="1"/>
@@ -1625,8 +1623,11 @@
       <c r="O26" s="1"/>
     </row>
     <row r="27" ht="63">
+      <c r="B27" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="J27" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/自考本科/承办主考学校/主考学校对比.xlsx
+++ b/自考本科/承办主考学校/主考学校对比.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>深圳大学</t>
   </si>
@@ -114,18 +114,21 @@
     <t>考试大纲</t>
   </si>
   <si>
+    <t>是（参考教材）</t>
+  </si>
+  <si>
     <t>是否开卷考试（能带教材）</t>
   </si>
   <si>
     <t>全部开卷</t>
   </si>
   <si>
+    <t>闭卷</t>
+  </si>
+  <si>
     <t>纸笔开卷</t>
   </si>
   <si>
-    <t>闭卷</t>
-  </si>
-  <si>
     <t>部分开卷</t>
   </si>
   <si>
@@ -168,8 +171,10 @@
     <t>毕业论文报考方式</t>
   </si>
   <si>
-    <t xml:space="preserve">毕业申请方式
-（统一为广东教育考试院）</t>
+    <t>毕业申请方式</t>
+  </si>
+  <si>
+    <t>（统一为广东教育考试院）</t>
   </si>
   <si>
     <t>学位</t>
@@ -251,6 +256,15 @@
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>要求最低</t>
+  </si>
+  <si>
+    <t>全程线上提交资料</t>
+  </si>
+  <si>
+    <t>理论毕业时间最短</t>
   </si>
   <si>
     <t>今年下半年才新开考计算机实践，新学校容易踩坑</t>
@@ -260,7 +274,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -272,6 +286,17 @@
       <color theme="1"/>
       <name val="等距更纱黑体 SC Light"/>
     </font>
+    <font>
+      <sz val="8.000000"/>
+      <color theme="1"/>
+      <name val="等距更纱黑体 SC Light"/>
+    </font>
+    <font>
+      <sz val="8.000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -282,20 +307,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="6" tint="0"/>
+        <bgColor theme="6" tint="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -320,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -335,20 +360,32 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="1" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -358,11 +395,14 @@
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="1" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="1" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -871,30 +911,30 @@
   </cols>
   <sheetData>
     <row r="1" s="3" customFormat="1" ht="15.75">
-      <c r="A1" s="3"/>
+      <c r="A1" s="4"/>
       <c r="B1" s="4"/>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="K1" s="3"/>
@@ -904,34 +944,34 @@
       <c r="O1" s="3"/>
     </row>
     <row r="2" ht="15.75">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K2" s="1"/>
@@ -942,318 +982,332 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" ht="15.75">
-      <c r="A3" s="6"/>
+      <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="15.75">
-      <c r="A4" s="6"/>
+      <c r="A4" s="7"/>
       <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" ht="15.75">
-      <c r="A5" s="6"/>
+      <c r="A5" s="7"/>
       <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" ht="15.75">
-      <c r="A6" s="6"/>
+      <c r="A6" s="7"/>
       <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" ht="15.75">
-      <c r="A7" s="6"/>
+      <c r="A7" s="7"/>
       <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" ht="31.5">
+      <c r="A8" s="7"/>
+      <c r="B8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" ht="31.5">
-      <c r="A8" s="6"/>
-      <c r="B8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="J8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="1" t="s">
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" ht="7.0999999999999996" customHeight="1">
+      <c r="A9" s="7"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" s="11" customFormat="1" ht="9.5500000000000007" customHeight="1">
+      <c r="A10" s="12"/>
+      <c r="B10" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+    </row>
+    <row r="11" s="11" customFormat="1" ht="9.5500000000000007" customHeight="1">
+      <c r="A11" s="12"/>
+      <c r="B11" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13">
+        <v>1800</v>
+      </c>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+    </row>
+    <row r="12" s="11" customFormat="1" ht="9.5500000000000007" customHeight="1">
+      <c r="A12" s="12"/>
+      <c r="B12" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+    </row>
+    <row r="13" s="14" customFormat="1" ht="15.75">
+      <c r="A13" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="15.75">
+      <c r="A14" s="7"/>
+      <c r="B14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1500</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1500</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" ht="15.75">
-      <c r="A9" s="6"/>
-    </row>
-    <row r="10" ht="15.75">
-      <c r="A10" s="6"/>
-      <c r="B10" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-    </row>
-    <row r="11" ht="15.75">
-      <c r="A11" s="6"/>
-      <c r="B11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1">
-        <v>1800</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" ht="15.75">
-      <c r="A12" s="6"/>
-      <c r="B12" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-    </row>
-    <row r="13" s="10" customFormat="1" ht="15.75">
-      <c r="A13" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="15.75">
-      <c r="A14" s="6"/>
-      <c r="B14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="1">
+      <c r="G14" s="8">
+        <v>800</v>
+      </c>
+      <c r="H14" s="2">
         <v>1500</v>
       </c>
-      <c r="D14" s="1">
+      <c r="I14" s="2">
         <v>1000</v>
       </c>
-      <c r="E14" s="1">
-        <v>1500</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="7">
-        <v>800</v>
-      </c>
-      <c r="H14" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I14" s="1">
-        <v>1000</v>
-      </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K14" s="1"/>
@@ -1264,22 +1318,22 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="15.75">
-      <c r="A15" s="6"/>
+      <c r="A15" s="7"/>
       <c r="B15" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
+      <c r="D15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -1288,32 +1342,32 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="15.75">
-      <c r="A16" s="6"/>
+      <c r="A16" s="7"/>
       <c r="B16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K16" s="1"/>
@@ -1322,150 +1376,152 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="47.25">
-      <c r="A17" s="6"/>
+    <row r="17" s="1" customFormat="1" ht="15.75">
+      <c r="A17" s="7"/>
       <c r="B17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
+        <v>51</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" s="10" customFormat="1" ht="15.75">
-      <c r="A18" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="13">
+    <row r="18" s="14" customFormat="1" ht="15.75">
+      <c r="A18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="17">
         <v>60</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="16">
         <v>70</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="16">
         <v>65</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="16">
         <v>70</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="16">
         <v>70</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="16">
         <v>60</v>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
     </row>
     <row r="19" ht="15.75">
-      <c r="A19" s="6"/>
+      <c r="A19" s="7"/>
       <c r="B19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="1">
+        <v>55</v>
+      </c>
+      <c r="C19" s="8">
         <v>70</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="8">
         <v>70</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" s="1">
+      <c r="E19" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="2">
         <v>70</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I19" s="1" t="s">
+      <c r="G19" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>56</v>
+      <c r="H19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="15.75">
-      <c r="A20" s="6"/>
+      <c r="A20" s="7"/>
       <c r="B20" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="1" t="s">
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" ht="15.75">
-      <c r="A21" s="6"/>
+      <c r="A21" s="7"/>
       <c r="B21" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="1">
+        <v>60</v>
+      </c>
+      <c r="C21" s="2">
         <v>20</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="2">
         <v>30</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="10">
         <v>10</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21" s="2">
         <v>25</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="2">
         <v>30</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="2">
         <v>25</v>
       </c>
       <c r="K21" s="1"/>
@@ -1476,90 +1532,90 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" ht="15.75">
-      <c r="A22" s="6"/>
+      <c r="A22" s="7"/>
       <c r="B22" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" s="10" customFormat="1" ht="15.75">
-      <c r="A23" s="10"/>
-      <c r="B23" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="10" t="s">
+      <c r="J22" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" s="14" customFormat="1" ht="15.75">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="10" t="s">
+      <c r="D23" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="10" t="s">
+      <c r="G23" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
+      <c r="I23" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="63">
-      <c r="A24" s="1"/>
+      <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1569,26 +1625,26 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="94.5">
-      <c r="A25" s="1"/>
+      <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J25" s="1"/>
+      <c r="H25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J25" s="2"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -1597,25 +1653,26 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="47.25">
+      <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E26" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1" t="s">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="E26" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -1623,11 +1680,25 @@
       <c r="O26" s="1"/>
     </row>
     <row r="27" ht="63">
+      <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/自考本科/承办主考学校/主考学校对比.xlsx
+++ b/自考本科/承办主考学校/主考学校对比.xlsx
@@ -258,7 +258,31 @@
     <t>备注</t>
   </si>
   <si>
-    <t>要求最低</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t xml:space="preserve">要求最低
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="2"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t>注意！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t>官网公布报考信息的时间通常非常紧张，往往是开始报考前一天，注意邮寄资料的时间</t>
+    </r>
   </si>
   <si>
     <t>全程线上提交资料</t>
@@ -1679,7 +1703,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" ht="63">
+    <row r="27" ht="126">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
         <v>78</v>
